--- a/output/pdf_financials_xlsx/FW.xlsx
+++ b/output/pdf_financials_xlsx/FW.xlsx
@@ -655,13 +655,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>7.7953</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>7.114942</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>8.682295999999999</v>
       </c>
       <c r="E12" s="1" t="inlineStr">
         <is>
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.919728</v>
+        <v>-0.875572</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.047054</v>
+        <v>-7.161996</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.398531</v>
+        <v>-10.080827</v>
       </c>
       <c r="E27" s="1" t="inlineStr">
         <is>
@@ -1030,13 +1030,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.956637</v>
+        <v>-0.838663</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.021947</v>
+        <v>-7.136889</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.397861</v>
+        <v>-10.080157</v>
       </c>
       <c r="E29" s="1" t="inlineStr">
         <is>
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>67.56564319982409</v>
+        <v>-8.145430762435076</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-0.3754897431949221</v>
+        <v>-122.1045526869579</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-15.021624478355</v>
+        <v>-108.3228827021152</v>
       </c>
       <c r="E30" s="1" t="inlineStr">
         <is>
@@ -1127,10 +1127,10 @@
         <v>5.222829</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>2.365287</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.987089</v>
       </c>
     </row>
     <row r="35">
@@ -1165,10 +1165,10 @@
         <v>5.222829</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>2.365287</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.987089</v>
       </c>
     </row>
     <row r="37">
@@ -1393,10 +1393,10 @@
         <v>22.39487</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>13.959236</v>
+        <v>11.593949</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>12.278841</v>
+        <v>10.291752</v>
       </c>
     </row>
     <row r="49">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4274,7 +4274,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E212" s="5" t="n">

--- a/output/pdf_financials_xlsx/FW.xlsx
+++ b/output/pdf_financials_xlsx/FW.xlsx
@@ -1762,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>1.177066</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.5683319999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5248,7 +5248,11 @@
           <t>Net Income (loss) $ 947,703 $</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -7792,7 +7796,11 @@
           <t>Net income (loss) $</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E129" s="5" t="n">
         <v>14.51072</v>
       </c>
